--- a/data/trans_orig/Q5416-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5416-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12014</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>928</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>282215</t>
+          <t>281696</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>290923</t>
+          <t>290811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>324289</t>
+          <t>324513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>337423</t>
+          <t>337273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>611795</t>
+          <t>610837</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>627246</t>
+          <t>626886</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13565</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26971</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>16001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36193</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>193965</t>
+          <t>192653</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>205508</t>
+          <t>205142</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>295865</t>
+          <t>294594</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>316596</t>
+          <t>316387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>495462</t>
+          <t>494308</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>518833</t>
+          <t>518525</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21080</t>
+          <t>21256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18310</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32747</t>
+          <t>32500</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>21365</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>43671</t>
+          <t>43343</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>480822</t>
+          <t>480006</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>494332</t>
+          <t>494104</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>625528</t>
+          <t>626168</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>649966</t>
+          <t>649874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1112749</t>
+          <t>1113102</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1140217</t>
+          <t>1140342</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>937</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13945</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15697</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17269</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>295517</t>
+          <t>295264</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>306552</t>
+          <t>306701</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>334691</t>
+          <t>335357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>348125</t>
+          <t>348887</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>635772</t>
+          <t>636036</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>651988</t>
+          <t>651961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>10984</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36774</t>
+          <t>37175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19384</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43158</t>
+          <t>43077</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38224</t>
+          <t>37340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26722</t>
+          <t>26533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51093</t>
+          <t>49789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>11617</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>17530</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>219978</t>
+          <t>220058</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>239187</t>
+          <t>239058</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>318270</t>
+          <t>316551</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>346408</t>
+          <t>345852</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>545756</t>
+          <t>547271</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>580014</t>
+          <t>580927</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18219</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38533</t>
+          <t>39001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26417</t>
+          <t>26025</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50890</t>
+          <t>50740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>25773</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49031</t>
+          <t>49933</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>34310</t>
+          <t>35247</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>62494</t>
+          <t>62008</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12403</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10961</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>18815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>523398</t>
+          <t>521963</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>543478</t>
+          <t>543602</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>658809</t>
+          <t>658248</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>690999</t>
+          <t>691399</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1189535</t>
+          <t>1191203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1227225</t>
+          <t>1227944</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4805,12 +4805,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>321625</t>
+          <t>320907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>332338</t>
+          <t>332330</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>356327</t>
+          <t>358294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>371995</t>
+          <t>372866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>684723</t>
+          <t>685189</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>702943</t>
+          <t>702755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27756</t>
+          <t>28148</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22875</t>
+          <t>22062</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47090</t>
+          <t>47016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>33996</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63690</t>
+          <t>62090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -5402,12 +5402,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10453</t>
+          <t>10338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -5515,12 +5515,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>226696</t>
+          <t>227962</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>242874</t>
+          <t>243237</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>334331</t>
+          <t>333810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>363732</t>
+          <t>364774</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>569488</t>
+          <t>570613</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>603389</t>
+          <t>603564</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5600,12 +5600,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10901</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28742</t>
+          <t>28139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>26297</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60317</t>
+          <t>61120</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>47758</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>79493</t>
+          <t>80679</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -5971,12 +5971,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>12418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -6084,12 +6084,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>554846</t>
+          <t>554171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>573479</t>
+          <t>573445</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>700565</t>
+          <t>699178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>734403</t>
+          <t>734111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1262250</t>
+          <t>1263226</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1300275</t>
+          <t>1300276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6574,67 +6574,67 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2220</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5767</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5886</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -6652,32 +6652,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7808</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6687,32 +6687,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6722,32 +6722,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>14050</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>20620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>656</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6800,67 +6800,67 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2596</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>6518</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>5424</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -6878,32 +6878,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>363651</t>
+          <t>402435</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>358447</t>
+          <t>397516</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>366197</t>
+          <t>404861</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>595647</t>
+          <t>424513</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>586065</t>
+          <t>417884</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>603249</t>
+          <t>429078</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6948,32 +6948,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>959299</t>
+          <t>826948</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951377</t>
+          <t>819796</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>968376</t>
+          <t>832785</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -6991,17 +6991,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7026,17 +7026,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7061,17 +7061,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7108,32 +7108,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7143,32 +7143,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>14687</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>21447</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7178,32 +7178,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>19369</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>13578</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>27283</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -7221,32 +7221,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14295</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7256,32 +7256,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35406</t>
+          <t>38467</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27864</t>
+          <t>29665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44131</t>
+          <t>48103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7291,32 +7291,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43314</t>
+          <t>47193</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35151</t>
+          <t>38128</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53574</t>
+          <t>59173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -7334,32 +7334,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>19675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -7447,32 +7447,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>267647</t>
+          <t>293082</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>260089</t>
+          <t>285579</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>272675</t>
+          <t>298762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7482,32 +7482,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>368920</t>
+          <t>402702</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>358625</t>
+          <t>391229</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>378953</t>
+          <t>414207</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>636567</t>
+          <t>695783</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>682111</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>646795</t>
+          <t>708296</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -7560,17 +7560,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7595,17 +7595,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>707844</t>
+          <t>773920</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>707844</t>
+          <t>773920</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>707844</t>
+          <t>773920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7677,32 +7677,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>11367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>23101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29043</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -7790,32 +7790,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18045</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7825,32 +7825,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44809</t>
+          <t>49139</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23194</t>
+          <t>39861</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60898</t>
+          <t>61319</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>55935</t>
+          <t>61243</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>34796</t>
+          <t>50017</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>70411</t>
+          <t>75451</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -7903,32 +7903,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7938,32 +7938,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7973,32 +7973,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19022</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -8016,32 +8016,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>631298</t>
+          <t>695516</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>623232</t>
+          <t>686842</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>637518</t>
+          <t>701867</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8051,32 +8051,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>964567</t>
+          <t>827214</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>941764</t>
+          <t>814699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>998187</t>
+          <t>839662</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8086,32 +8086,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1595866</t>
+          <t>1522732</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1577639</t>
+          <t>1505590</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1629348</t>
+          <t>1536690</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -8129,17 +8129,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8164,17 +8164,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8199,17 +8199,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
